--- a/entregables_barranquita/METRADO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/METRADO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -906,7 +906,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>EXPEDIENTE TÉCNICO</t>
+          <t>SERVICIO DE DISEÑO - DRENAJE PLUVIAL</t>
         </is>
       </c>
     </row>
